--- a/reports/pro-crypto/pro-crypto-bundler-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-bundler-report.xlsx
@@ -83,6 +83,18 @@
     <x:t>MENLO PARK</x:t>
   </x:si>
   <x:si>
+    <x:t>C00848440</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PROTECT PROGRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00835959</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FAIRSHAKE</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00836221</x:t>
   </x:si>
   <x:si>
@@ -104,24 +116,15 @@
     <x:t>KEEP STARTUPS IN AMERICA</x:t>
   </x:si>
   <x:si>
-    <x:t>C00835959</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FAIRSHAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00848440</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PROTECT PROGRESS</x:t>
-  </x:si>
-  <x:si>
     <x:t>BRIAN</x:t>
   </x:si>
   <x:si>
     <x:t>ARMSTRONG</x:t>
   </x:si>
   <x:si>
+    <x:t>SAN FRANCISCO</x:t>
+  </x:si>
+  <x:si>
     <x:t>PALO ALTO</x:t>
   </x:si>
   <x:si>
@@ -129,9 +132,6 @@
   </x:si>
   <x:si>
     <x:t>REPUBLICANS FOR A PRO-CRYPTO SENATE MAJORITY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAN FRANCISCO</x:t>
   </x:si>
   <x:si>
     <x:t>LAURA</x:t>
@@ -7496,19 +7496,19 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
+      <x:c r="F6" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
       <x:c r="G6" s="0">
-        <x:v>5000</x:v>
+        <x:v>33500000</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
@@ -7519,19 +7519,19 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="G7" s="0">
-        <x:v>10000</x:v>
+        <x:v>875000</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
@@ -7542,7 +7542,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>10</x:v>
@@ -7554,7 +7554,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>33500000</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
@@ -7565,7 +7565,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
         <x:v>10</x:v>
@@ -7577,7 +7577,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>875000</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
@@ -7588,19 +7588,19 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>23300</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
@@ -7611,19 +7611,19 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>20000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
@@ -7634,19 +7634,19 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="E12" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="F12" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
       <x:c r="G12" s="0">
-        <x:v>1000000</x:v>
+        <x:v>23300</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
@@ -7657,16 +7657,16 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G13" s="0">
         <x:v>5000</x:v>
@@ -7680,16 +7680,16 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="G14" s="0">
         <x:v>10000</x:v>
@@ -7795,16 +7795,16 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G19" s="0">
         <x:v>1000</x:v>
@@ -7824,10 +7824,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G20" s="0">
         <x:v>1500</x:v>
@@ -7864,16 +7864,16 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G22" s="0">
         <x:v>250</x:v>
@@ -7893,10 +7893,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G23" s="0">
         <x:v>1000</x:v>
@@ -8008,10 +8008,10 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G28" s="0">
         <x:v>250</x:v>
@@ -8077,10 +8077,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G31" s="0">
         <x:v>1500</x:v>
@@ -8100,10 +8100,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G32" s="0">
         <x:v>500</x:v>
@@ -8123,10 +8123,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G33" s="0">
         <x:v>1500</x:v>
@@ -8192,10 +8192,10 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G36" s="0">
         <x:v>13200</x:v>
@@ -8209,16 +8209,16 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E37" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G37" s="0">
         <x:v>1000</x:v>
@@ -8261,10 +8261,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G39" s="0">
         <x:v>680</x:v>
@@ -8330,10 +8330,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="E42" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F42" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G42" s="0">
         <x:v>250000</x:v>
@@ -8353,10 +8353,10 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="E43" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F43" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G43" s="0">
         <x:v>13200</x:v>
@@ -8399,10 +8399,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="E45" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F45" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G45" s="0">
         <x:v>250</x:v>
@@ -8514,10 +8514,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="E50" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F50" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G50" s="0">
         <x:v>20000</x:v>
@@ -8554,16 +8554,16 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E52" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F52" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G52" s="0">
         <x:v>500000</x:v>
@@ -8606,10 +8606,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="E54" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F54" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G54" s="0">
         <x:v>500</x:v>
@@ -8652,10 +8652,10 @@
         <x:v>149</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F56" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G56" s="0">
         <x:v>250</x:v>
@@ -8669,16 +8669,16 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E57" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F57" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="G57" s="0">
         <x:v>10000</x:v>
@@ -8744,10 +8744,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="E60" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F60" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G60" s="0">
         <x:v>13200</x:v>
@@ -8767,10 +8767,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="E61" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F61" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G61" s="0">
         <x:v>2500</x:v>
@@ -8784,16 +8784,16 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E62" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F62" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G62" s="0">
         <x:v>250000</x:v>
@@ -9037,16 +9037,16 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E73" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F73" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G73" s="0">
         <x:v>250000</x:v>
@@ -9066,10 +9066,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="E74" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F74" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G74" s="0">
         <x:v>13200</x:v>
@@ -9129,16 +9129,16 @@
         <x:v>192</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E77" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F77" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G77" s="0">
         <x:v>25000</x:v>
@@ -9227,10 +9227,10 @@
         <x:v>202</x:v>
       </x:c>
       <x:c r="E81" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F81" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G81" s="0">
         <x:v>250</x:v>
@@ -9319,10 +9319,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="E85" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F85" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G85" s="0">
         <x:v>1500</x:v>
@@ -9388,10 +9388,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="E88" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F88" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G88" s="0">
         <x:v>13200</x:v>
@@ -9411,10 +9411,10 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="E89" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F89" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G89" s="0">
         <x:v>1000</x:v>
@@ -9480,10 +9480,10 @@
         <x:v>227</x:v>
       </x:c>
       <x:c r="E92" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F92" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="G92" s="0">
         <x:v>10000</x:v>
@@ -9503,10 +9503,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="E93" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F93" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G93" s="0">
         <x:v>875000</x:v>
@@ -9526,10 +9526,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="E94" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F94" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G94" s="0">
         <x:v>33500000</x:v>
@@ -9549,10 +9549,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F95" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G95" s="0">
         <x:v>875000</x:v>
@@ -9572,10 +9572,10 @@
         <x:v>227</x:v>
       </x:c>
       <x:c r="E96" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F96" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G96" s="0">
         <x:v>5000</x:v>
@@ -9595,10 +9595,10 @@
         <x:v>227</x:v>
       </x:c>
       <x:c r="E97" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F97" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G97" s="0">
         <x:v>5000</x:v>
@@ -9618,10 +9618,10 @@
         <x:v>227</x:v>
       </x:c>
       <x:c r="E98" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F98" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="G98" s="0">
         <x:v>10000</x:v>
@@ -9635,16 +9635,16 @@
         <x:v>231</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E99" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F99" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G99" s="0">
         <x:v>10000</x:v>
@@ -9658,16 +9658,16 @@
         <x:v>232</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E100" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F100" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G100" s="0">
         <x:v>250000</x:v>
@@ -9687,10 +9687,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="E101" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F101" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G101" s="0">
         <x:v>500</x:v>
@@ -9733,10 +9733,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="E103" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F103" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G103" s="0">
         <x:v>12500</x:v>
@@ -9756,10 +9756,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="E104" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F104" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G104" s="0">
         <x:v>5000</x:v>
@@ -9779,10 +9779,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="E105" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F105" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G105" s="0">
         <x:v>100000</x:v>
@@ -9802,10 +9802,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="E106" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F106" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G106" s="0">
         <x:v>12500</x:v>
@@ -9825,10 +9825,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="E107" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F107" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G107" s="0">
         <x:v>13200</x:v>
@@ -9871,10 +9871,10 @@
         <x:v>243</x:v>
       </x:c>
       <x:c r="E109" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F109" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G109" s="0">
         <x:v>5000</x:v>
@@ -9894,10 +9894,10 @@
         <x:v>243</x:v>
       </x:c>
       <x:c r="E110" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F110" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G110" s="0">
         <x:v>1500</x:v>
@@ -9940,10 +9940,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="E112" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F112" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G112" s="0">
         <x:v>5000</x:v>
@@ -9963,10 +9963,10 @@
         <x:v>243</x:v>
       </x:c>
       <x:c r="E113" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F113" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G113" s="0">
         <x:v>250</x:v>
@@ -9986,10 +9986,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="E114" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F114" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G114" s="0">
         <x:v>1500</x:v>
@@ -10101,10 +10101,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="E119" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F119" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G119" s="0">
         <x:v>500</x:v>
@@ -10124,10 +10124,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="E120" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F120" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G120" s="0">
         <x:v>300</x:v>
@@ -10216,10 +10216,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="E124" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F124" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G124" s="0">
         <x:v>250</x:v>
@@ -10239,10 +10239,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="E125" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F125" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G125" s="0">
         <x:v>500</x:v>
@@ -10285,10 +10285,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="E127" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F127" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G127" s="0">
         <x:v>5000</x:v>
@@ -10331,10 +10331,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="E129" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F129" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G129" s="0">
         <x:v>1000</x:v>
@@ -10354,10 +10354,10 @@
         <x:v>289</x:v>
       </x:c>
       <x:c r="E130" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F130" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G130" s="0">
         <x:v>250</x:v>
@@ -10423,10 +10423,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="E133" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F133" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G133" s="0">
         <x:v>1000</x:v>
@@ -10440,16 +10440,16 @@
         <x:v>298</x:v>
       </x:c>
       <x:c r="C134" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D134" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E134" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F134" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G134" s="0">
         <x:v>10000</x:v>
@@ -10492,10 +10492,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="E136" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F136" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G136" s="0">
         <x:v>1995942</x:v>
@@ -10699,10 +10699,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="E145" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F145" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G145" s="0">
         <x:v>12500</x:v>
@@ -10728,7 +10728,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="G146" s="0">
-        <x:v>100000</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:7">
@@ -10745,13 +10745,13 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="E147" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F147" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G147" s="0">
-        <x:v>5000</x:v>
+        <x:v>12500</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:7">
@@ -10768,13 +10768,13 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="E148" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F148" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G148" s="0">
-        <x:v>12500</x:v>
+        <x:v>100000</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:7">
@@ -10791,10 +10791,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="E149" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F149" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G149" s="0">
         <x:v>1500</x:v>
@@ -10814,10 +10814,10 @@
         <x:v>227</x:v>
       </x:c>
       <x:c r="E150" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F150" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G150" s="0">
         <x:v>13200</x:v>
@@ -10837,10 +10837,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="E151" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F151" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G151" s="0">
         <x:v>13200</x:v>
@@ -10860,10 +10860,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="E152" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F152" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G152" s="0">
         <x:v>500</x:v>
@@ -10883,10 +10883,10 @@
         <x:v>117</x:v>
       </x:c>
       <x:c r="E153" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F153" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G153" s="0">
         <x:v>13200</x:v>
@@ -10952,13 +10952,13 @@
         <x:v>336</x:v>
       </x:c>
       <x:c r="E156" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F156" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G156" s="0">
-        <x:v>5000</x:v>
+        <x:v>26400</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:7">
@@ -10998,13 +10998,13 @@
         <x:v>336</x:v>
       </x:c>
       <x:c r="E158" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="F158" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="G158" s="0">
-        <x:v>26400</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:7">
@@ -11038,16 +11038,16 @@
         <x:v>339</x:v>
       </x:c>
       <x:c r="C160" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D160" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E160" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F160" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="G160" s="0">
         <x:v>10000</x:v>
@@ -11067,10 +11067,10 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="E161" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F161" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G161" s="0">
         <x:v>5000</x:v>
@@ -11090,10 +11090,10 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="E162" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F162" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G162" s="0">
         <x:v>5000</x:v>
@@ -11107,16 +11107,16 @@
         <x:v>343</x:v>
       </x:c>
       <x:c r="C163" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D163" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E163" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F163" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G163" s="0">
         <x:v>250000</x:v>
@@ -11136,10 +11136,10 @@
         <x:v>347</x:v>
       </x:c>
       <x:c r="E164" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F164" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G164" s="0">
         <x:v>2525</x:v>
@@ -11153,16 +11153,16 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="C165" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D165" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E165" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F165" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G165" s="0">
         <x:v>50000</x:v>
@@ -11176,16 +11176,16 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="C166" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D166" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E166" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F166" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G166" s="0">
         <x:v>50000</x:v>
@@ -11228,10 +11228,10 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="E168" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F168" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G168" s="0">
         <x:v>11250</x:v>
@@ -11251,10 +11251,10 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="E169" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F169" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G169" s="0">
         <x:v>15000</x:v>
@@ -11297,10 +11297,10 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="E171" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F171" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G171" s="0">
         <x:v>500</x:v>
@@ -11366,10 +11366,10 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="E174" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F174" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G174" s="0">
         <x:v>1500</x:v>
@@ -11435,10 +11435,10 @@
         <x:v>243</x:v>
       </x:c>
       <x:c r="E177" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F177" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G177" s="0">
         <x:v>1500</x:v>
@@ -11458,10 +11458,10 @@
         <x:v>243</x:v>
       </x:c>
       <x:c r="E178" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F178" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G178" s="0">
         <x:v>5000</x:v>
@@ -11504,10 +11504,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="E180" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F180" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G180" s="0">
         <x:v>500</x:v>
@@ -11527,10 +11527,10 @@
         <x:v>380</x:v>
       </x:c>
       <x:c r="E181" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F181" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G181" s="0">
         <x:v>500</x:v>
@@ -11573,10 +11573,10 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="E183" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F183" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G183" s="0">
         <x:v>100000</x:v>
@@ -11596,10 +11596,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="E184" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F184" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G184" s="0">
         <x:v>1047540</x:v>
@@ -11619,10 +11619,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="E185" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F185" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G185" s="0">
         <x:v>50000</x:v>
@@ -11642,10 +11642,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="E186" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F186" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G186" s="0">
         <x:v>50000</x:v>
@@ -11665,10 +11665,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="E187" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F187" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G187" s="0">
         <x:v>2450000</x:v>
@@ -11711,13 +11711,13 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="E189" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="F189" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="G189" s="0">
-        <x:v>2450000</x:v>
+        <x:v>510044</x:v>
       </x:c>
     </x:row>
     <x:row r="190" spans="1:7">
@@ -11734,13 +11734,13 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="E190" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F190" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G190" s="0">
-        <x:v>510044</x:v>
+        <x:v>2450000</x:v>
       </x:c>
     </x:row>
     <x:row r="191" spans="1:7">
@@ -11757,10 +11757,10 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="E191" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F191" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G191" s="0">
         <x:v>13200</x:v>
@@ -11849,10 +11849,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="E195" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F195" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G195" s="0">
         <x:v>2500</x:v>
@@ -11872,10 +11872,10 @@
         <x:v>243</x:v>
       </x:c>
       <x:c r="E196" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F196" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G196" s="0">
         <x:v>1000</x:v>
@@ -12080,7 +12080,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>10</x:v>
@@ -12097,7 +12097,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
         <x:v>10</x:v>
@@ -12131,7 +12131,7 @@
         <x:v>343</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
         <x:v>10</x:v>
@@ -12165,7 +12165,7 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
         <x:v>10</x:v>
@@ -12199,7 +12199,7 @@
         <x:v>232</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
         <x:v>10</x:v>
@@ -12216,7 +12216,7 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
         <x:v>10</x:v>
@@ -12335,7 +12335,7 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
         <x:v>10</x:v>
@@ -12369,7 +12369,7 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
         <x:v>10</x:v>
@@ -12471,7 +12471,7 @@
         <x:v>192</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
         <x:v>10</x:v>
@@ -12488,7 +12488,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
         <x:v>10</x:v>
@@ -12641,7 +12641,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
         <x:v>10</x:v>
@@ -12692,7 +12692,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
         <x:v>10</x:v>
@@ -12964,7 +12964,7 @@
         <x:v>339</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
         <x:v>10</x:v>
@@ -13015,7 +13015,7 @@
         <x:v>298</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
         <x:v>10</x:v>
@@ -13032,7 +13032,7 @@
         <x:v>231</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
         <x:v>10</x:v>
@@ -13049,7 +13049,7 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
         <x:v>10</x:v>
@@ -14103,7 +14103,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C127" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
         <x:v>10</x:v>
@@ -14120,7 +14120,7 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="C128" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
         <x:v>10</x:v>
@@ -14936,7 +14936,7 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="C176" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D176" s="0" t="s">
         <x:v>10</x:v>
@@ -15110,7 +15110,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
         <x:v>10</x:v>
@@ -15133,7 +15133,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
         <x:v>10</x:v>
@@ -15156,7 +15156,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
         <x:v>10</x:v>
@@ -15179,7 +15179,7 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
         <x:v>10</x:v>
@@ -15294,7 +15294,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
         <x:v>10</x:v>
@@ -15363,7 +15363,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
         <x:v>10</x:v>
@@ -15409,7 +15409,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
         <x:v>10</x:v>
@@ -15432,7 +15432,7 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
         <x:v>10</x:v>
@@ -15570,7 +15570,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
         <x:v>10</x:v>
@@ -15639,7 +15639,7 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
         <x:v>10</x:v>
@@ -15800,7 +15800,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G34" s="0" t="s">
         <x:v>10</x:v>
@@ -15846,7 +15846,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G36" s="0" t="s">
         <x:v>10</x:v>
@@ -15869,7 +15869,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G37" s="0" t="s">
         <x:v>10</x:v>
@@ -15961,7 +15961,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G41" s="0" t="s">
         <x:v>10</x:v>
@@ -16145,7 +16145,7 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="F49" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G49" s="0" t="s">
         <x:v>10</x:v>
@@ -16168,7 +16168,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F50" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G50" s="0" t="s">
         <x:v>10</x:v>
@@ -16214,7 +16214,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F52" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G52" s="0" t="s">
         <x:v>10</x:v>
@@ -16237,7 +16237,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F53" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G53" s="0" t="s">
         <x:v>10</x:v>
@@ -16260,7 +16260,7 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="F54" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G54" s="0" t="s">
         <x:v>10</x:v>
@@ -16329,7 +16329,7 @@
         <x:v>339</x:v>
       </x:c>
       <x:c r="F57" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G57" s="0" t="s">
         <x:v>10</x:v>
@@ -16398,7 +16398,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F60" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G60" s="0" t="s">
         <x:v>10</x:v>
@@ -16582,7 +16582,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F68" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G68" s="0" t="s">
         <x:v>10</x:v>
@@ -16605,7 +16605,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F69" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G69" s="0" t="s">
         <x:v>10</x:v>
@@ -16628,7 +16628,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F70" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G70" s="0" t="s">
         <x:v>10</x:v>
@@ -16927,7 +16927,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F83" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G83" s="0" t="s">
         <x:v>10</x:v>
@@ -16950,7 +16950,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F84" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G84" s="0" t="s">
         <x:v>10</x:v>
@@ -17088,7 +17088,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F90" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G90" s="0" t="s">
         <x:v>10</x:v>
@@ -18870,7 +18870,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
         <x:v>10</x:v>
@@ -19031,7 +19031,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
         <x:v>10</x:v>
@@ -19054,7 +19054,7 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
         <x:v>10</x:v>
@@ -19077,7 +19077,7 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
         <x:v>10</x:v>
@@ -19146,7 +19146,7 @@
         <x:v>231</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
         <x:v>10</x:v>
@@ -19169,7 +19169,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
         <x:v>10</x:v>
@@ -19261,7 +19261,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
         <x:v>10</x:v>
@@ -19284,7 +19284,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
         <x:v>10</x:v>
@@ -19468,7 +19468,7 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G31" s="0" t="s">
         <x:v>10</x:v>
@@ -19491,7 +19491,7 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G32" s="0" t="s">
         <x:v>10</x:v>
@@ -19790,7 +19790,7 @@
         <x:v>339</x:v>
       </x:c>
       <x:c r="F45" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G45" s="0" t="s">
         <x:v>10</x:v>
@@ -19951,7 +19951,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F52" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G52" s="0" t="s">
         <x:v>10</x:v>
@@ -19974,7 +19974,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F53" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G53" s="0" t="s">
         <x:v>10</x:v>
@@ -19997,7 +19997,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F54" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G54" s="0" t="s">
         <x:v>10</x:v>
@@ -20020,7 +20020,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F55" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G55" s="0" t="s">
         <x:v>10</x:v>
@@ -20273,7 +20273,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F66" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G66" s="0" t="s">
         <x:v>10</x:v>
@@ -20296,7 +20296,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F67" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G67" s="0" t="s">
         <x:v>10</x:v>
@@ -20319,7 +20319,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F68" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G68" s="0" t="s">
         <x:v>10</x:v>
@@ -20342,7 +20342,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F69" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G69" s="0" t="s">
         <x:v>10</x:v>
@@ -20365,7 +20365,7 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="F70" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G70" s="0" t="s">
         <x:v>10</x:v>
@@ -20503,7 +20503,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F76" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G76" s="0" t="s">
         <x:v>10</x:v>
@@ -20526,7 +20526,7 @@
         <x:v>298</x:v>
       </x:c>
       <x:c r="F77" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G77" s="0" t="s">
         <x:v>10</x:v>
@@ -20572,7 +20572,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F79" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G79" s="0" t="s">
         <x:v>10</x:v>
@@ -20756,7 +20756,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F87" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G87" s="0" t="s">
         <x:v>10</x:v>
@@ -20779,7 +20779,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F88" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G88" s="0" t="s">
         <x:v>10</x:v>
@@ -20802,7 +20802,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F89" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G89" s="0" t="s">
         <x:v>10</x:v>
@@ -20894,7 +20894,7 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="F93" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G93" s="0" t="s">
         <x:v>10</x:v>
@@ -20917,7 +20917,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F94" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G94" s="0" t="s">
         <x:v>10</x:v>
@@ -20940,7 +20940,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F95" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G95" s="0" t="s">
         <x:v>10</x:v>
@@ -21147,7 +21147,7 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="F104" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G104" s="0" t="s">
         <x:v>10</x:v>
@@ -21216,7 +21216,7 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="F107" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G107" s="0" t="s">
         <x:v>10</x:v>
@@ -21561,7 +21561,7 @@
         <x:v>339</x:v>
       </x:c>
       <x:c r="F122" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G122" s="0" t="s">
         <x:v>10</x:v>
@@ -21791,7 +21791,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F132" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G132" s="0" t="s">
         <x:v>10</x:v>
@@ -21814,7 +21814,7 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="F133" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G133" s="0" t="s">
         <x:v>10</x:v>
@@ -21837,7 +21837,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F134" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G134" s="0" t="s">
         <x:v>10</x:v>
@@ -22021,7 +22021,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F142" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G142" s="0" t="s">
         <x:v>10</x:v>
@@ -22044,7 +22044,7 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="F143" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G143" s="0" t="s">
         <x:v>10</x:v>
@@ -22067,7 +22067,7 @@
         <x:v>298</x:v>
       </x:c>
       <x:c r="F144" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G144" s="0" t="s">
         <x:v>10</x:v>
@@ -22090,7 +22090,7 @@
         <x:v>343</x:v>
       </x:c>
       <x:c r="F145" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G145" s="0" t="s">
         <x:v>10</x:v>
@@ -22136,7 +22136,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F147" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G147" s="0" t="s">
         <x:v>10</x:v>
@@ -22182,7 +22182,7 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="F149" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G149" s="0" t="s">
         <x:v>10</x:v>
@@ -22343,7 +22343,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F156" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G156" s="0" t="s">
         <x:v>10</x:v>
@@ -22458,7 +22458,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F161" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G161" s="0" t="s">
         <x:v>10</x:v>
@@ -22573,7 +22573,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F166" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G166" s="0" t="s">
         <x:v>10</x:v>
@@ -22711,7 +22711,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F172" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G172" s="0" t="s">
         <x:v>10</x:v>
@@ -22734,7 +22734,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F173" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G173" s="0" t="s">
         <x:v>10</x:v>
@@ -22803,7 +22803,7 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="F176" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G176" s="0" t="s">
         <x:v>10</x:v>
@@ -22826,7 +22826,7 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="F177" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G177" s="0" t="s">
         <x:v>10</x:v>
@@ -22849,7 +22849,7 @@
         <x:v>192</x:v>
       </x:c>
       <x:c r="F178" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G178" s="0" t="s">
         <x:v>10</x:v>
@@ -22918,7 +22918,7 @@
         <x:v>339</x:v>
       </x:c>
       <x:c r="F181" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G181" s="0" t="s">
         <x:v>10</x:v>
@@ -23056,7 +23056,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F187" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G187" s="0" t="s">
         <x:v>10</x:v>
@@ -23148,7 +23148,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F191" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G191" s="0" t="s">
         <x:v>10</x:v>
@@ -23171,7 +23171,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F192" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G192" s="0" t="s">
         <x:v>10</x:v>
@@ -23217,7 +23217,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F194" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G194" s="0" t="s">
         <x:v>10</x:v>
@@ -23263,7 +23263,7 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="F196" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G196" s="0" t="s">
         <x:v>10</x:v>
@@ -23378,7 +23378,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F201" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G201" s="0" t="s">
         <x:v>10</x:v>
@@ -23401,7 +23401,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F202" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G202" s="0" t="s">
         <x:v>10</x:v>
@@ -23470,7 +23470,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F205" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G205" s="0" t="s">
         <x:v>10</x:v>
@@ -23493,7 +23493,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F206" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G206" s="0" t="s">
         <x:v>10</x:v>
@@ -23654,7 +23654,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F213" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G213" s="0" t="s">
         <x:v>10</x:v>
@@ -23677,7 +23677,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F214" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G214" s="0" t="s">
         <x:v>10</x:v>
@@ -23838,7 +23838,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F221" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G221" s="0" t="s">
         <x:v>10</x:v>
@@ -23884,7 +23884,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F223" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G223" s="0" t="s">
         <x:v>10</x:v>
@@ -24022,7 +24022,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F229" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G229" s="0" t="s">
         <x:v>10</x:v>
@@ -24137,7 +24137,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F234" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G234" s="0" t="s">
         <x:v>10</x:v>
@@ -24160,7 +24160,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F235" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G235" s="0" t="s">
         <x:v>10</x:v>
@@ -24183,7 +24183,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F236" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G236" s="0" t="s">
         <x:v>10</x:v>
@@ -24206,7 +24206,7 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="F237" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G237" s="0" t="s">
         <x:v>10</x:v>
@@ -24321,7 +24321,7 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="F242" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G242" s="0" t="s">
         <x:v>10</x:v>
@@ -24390,7 +24390,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F245" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G245" s="0" t="s">
         <x:v>10</x:v>
@@ -24413,7 +24413,7 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="F246" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G246" s="0" t="s">
         <x:v>10</x:v>
@@ -24597,7 +24597,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F254" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G254" s="0" t="s">
         <x:v>10</x:v>
@@ -24620,7 +24620,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F255" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G255" s="0" t="s">
         <x:v>10</x:v>
@@ -24712,7 +24712,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F259" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G259" s="0" t="s">
         <x:v>10</x:v>
@@ -24758,7 +24758,7 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="F261" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G261" s="0" t="s">
         <x:v>10</x:v>
@@ -24965,7 +24965,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F270" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G270" s="0" t="s">
         <x:v>10</x:v>
@@ -25218,7 +25218,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F281" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G281" s="0" t="s">
         <x:v>10</x:v>
@@ -25241,7 +25241,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F282" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G282" s="0" t="s">
         <x:v>10</x:v>
@@ -25425,7 +25425,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F290" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G290" s="0" t="s">
         <x:v>10</x:v>
@@ -25448,7 +25448,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F291" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G291" s="0" t="s">
         <x:v>10</x:v>
@@ -25471,7 +25471,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F292" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G292" s="0" t="s">
         <x:v>10</x:v>
@@ -25517,7 +25517,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F294" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G294" s="0" t="s">
         <x:v>10</x:v>
@@ -25655,7 +25655,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F300" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G300" s="0" t="s">
         <x:v>10</x:v>
@@ -25885,7 +25885,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F310" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G310" s="0" t="s">
         <x:v>10</x:v>
@@ -25908,7 +25908,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F311" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G311" s="0" t="s">
         <x:v>10</x:v>
@@ -25931,7 +25931,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F312" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G312" s="0" t="s">
         <x:v>10</x:v>
@@ -26023,7 +26023,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F316" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G316" s="0" t="s">
         <x:v>10</x:v>
@@ -26046,7 +26046,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F317" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G317" s="0" t="s">
         <x:v>10</x:v>
@@ -26138,7 +26138,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F321" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G321" s="0" t="s">
         <x:v>10</x:v>
@@ -26161,7 +26161,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F322" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G322" s="0" t="s">
         <x:v>10</x:v>
@@ -26299,7 +26299,7 @@
         <x:v>339</x:v>
       </x:c>
       <x:c r="F328" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G328" s="0" t="s">
         <x:v>10</x:v>
@@ -26322,7 +26322,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F329" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G329" s="0" t="s">
         <x:v>10</x:v>
@@ -26391,7 +26391,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F332" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G332" s="0" t="s">
         <x:v>10</x:v>
@@ -26414,7 +26414,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F333" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G333" s="0" t="s">
         <x:v>10</x:v>
@@ -26437,7 +26437,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F334" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G334" s="0" t="s">
         <x:v>10</x:v>
@@ -26552,7 +26552,7 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="F339" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G339" s="0" t="s">
         <x:v>10</x:v>
@@ -26782,7 +26782,7 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="F349" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G349" s="0" t="s">
         <x:v>10</x:v>
@@ -26989,7 +26989,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F358" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G358" s="0" t="s">
         <x:v>10</x:v>
@@ -27012,7 +27012,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F359" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G359" s="0" t="s">
         <x:v>10</x:v>
@@ -27127,7 +27127,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F364" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G364" s="0" t="s">
         <x:v>10</x:v>
@@ -27173,7 +27173,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F366" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G366" s="0" t="s">
         <x:v>10</x:v>
@@ -27265,7 +27265,7 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="F370" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G370" s="0" t="s">
         <x:v>10</x:v>
@@ -27288,7 +27288,7 @@
         <x:v>231</x:v>
       </x:c>
       <x:c r="F371" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G371" s="0" t="s">
         <x:v>10</x:v>
@@ -27371,7 +27371,7 @@
         <x:v>745</x:v>
       </x:c>
       <x:c r="C375" s="0">
-        <x:v>4092</x:v>
+        <x:v>2100</x:v>
       </x:c>
       <x:c r="D375" s="0" t="s">
         <x:v>297</x:v>
@@ -27380,7 +27380,7 @@
         <x:v>298</x:v>
       </x:c>
       <x:c r="F375" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G375" s="0" t="s">
         <x:v>10</x:v>
@@ -27394,7 +27394,7 @@
         <x:v>745</x:v>
       </x:c>
       <x:c r="C376" s="0">
-        <x:v>2100</x:v>
+        <x:v>4092</x:v>
       </x:c>
       <x:c r="D376" s="0" t="s">
         <x:v>297</x:v>
@@ -27403,7 +27403,7 @@
         <x:v>298</x:v>
       </x:c>
       <x:c r="F376" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G376" s="0" t="s">
         <x:v>10</x:v>
@@ -27541,7 +27541,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F382" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G382" s="0" t="s">
         <x:v>10</x:v>
@@ -27587,7 +27587,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F384" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G384" s="0" t="s">
         <x:v>10</x:v>
@@ -27610,7 +27610,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F385" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G385" s="0" t="s">
         <x:v>10</x:v>
@@ -27725,7 +27725,7 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="F390" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G390" s="0" t="s">
         <x:v>10</x:v>
@@ -27748,7 +27748,7 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="F391" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G391" s="0" t="s">
         <x:v>10</x:v>
@@ -27771,7 +27771,7 @@
         <x:v>192</x:v>
       </x:c>
       <x:c r="F392" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G392" s="0" t="s">
         <x:v>10</x:v>
@@ -27886,7 +27886,7 @@
         <x:v>298</x:v>
       </x:c>
       <x:c r="F397" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G397" s="0" t="s">
         <x:v>10</x:v>
@@ -28047,7 +28047,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F404" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G404" s="0" t="s">
         <x:v>10</x:v>
@@ -28070,7 +28070,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F405" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G405" s="0" t="s">
         <x:v>10</x:v>
@@ -28093,7 +28093,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F406" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G406" s="0" t="s">
         <x:v>10</x:v>
@@ -28162,7 +28162,7 @@
         <x:v>339</x:v>
       </x:c>
       <x:c r="F409" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G409" s="0" t="s">
         <x:v>10</x:v>
@@ -28231,7 +28231,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F412" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G412" s="0" t="s">
         <x:v>10</x:v>
@@ -28277,7 +28277,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F414" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G414" s="0" t="s">
         <x:v>10</x:v>
@@ -28300,7 +28300,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F415" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G415" s="0" t="s">
         <x:v>10</x:v>
@@ -28323,7 +28323,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F416" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G416" s="0" t="s">
         <x:v>10</x:v>
@@ -28530,7 +28530,7 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="F425" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G425" s="0" t="s">
         <x:v>10</x:v>
@@ -28645,7 +28645,7 @@
         <x:v>231</x:v>
       </x:c>
       <x:c r="F430" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G430" s="0" t="s">
         <x:v>10</x:v>
@@ -28829,7 +28829,7 @@
         <x:v>339</x:v>
       </x:c>
       <x:c r="F438" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G438" s="0" t="s">
         <x:v>10</x:v>
@@ -28875,7 +28875,7 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="F440" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G440" s="0" t="s">
         <x:v>10</x:v>
@@ -29082,7 +29082,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F449" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G449" s="0" t="s">
         <x:v>10</x:v>
@@ -29151,7 +29151,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F452" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G452" s="0" t="s">
         <x:v>10</x:v>
@@ -29174,7 +29174,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F453" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G453" s="0" t="s">
         <x:v>10</x:v>
@@ -29427,7 +29427,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F464" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G464" s="0" t="s">
         <x:v>10</x:v>
@@ -29473,7 +29473,7 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="F466" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G466" s="0" t="s">
         <x:v>10</x:v>
@@ -29565,7 +29565,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F470" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G470" s="0" t="s">
         <x:v>10</x:v>
@@ -29588,7 +29588,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F471" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G471" s="0" t="s">
         <x:v>10</x:v>
@@ -29634,7 +29634,7 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="F473" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G473" s="0" t="s">
         <x:v>10</x:v>
@@ -29749,7 +29749,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F478" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G478" s="0" t="s">
         <x:v>10</x:v>
@@ -29795,7 +29795,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F480" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G480" s="0" t="s">
         <x:v>10</x:v>
@@ -29818,7 +29818,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F481" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G481" s="0" t="s">
         <x:v>10</x:v>
@@ -29864,7 +29864,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F483" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G483" s="0" t="s">
         <x:v>10</x:v>
@@ -29887,7 +29887,7 @@
         <x:v>192</x:v>
       </x:c>
       <x:c r="F484" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G484" s="0" t="s">
         <x:v>10</x:v>
@@ -29956,7 +29956,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F487" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G487" s="0" t="s">
         <x:v>10</x:v>
@@ -29979,7 +29979,7 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="F488" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G488" s="0" t="s">
         <x:v>10</x:v>
@@ -30094,7 +30094,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F493" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G493" s="0" t="s">
         <x:v>10</x:v>
@@ -30186,7 +30186,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F497" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G497" s="0" t="s">
         <x:v>10</x:v>
@@ -30209,7 +30209,7 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="F498" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G498" s="0" t="s">
         <x:v>10</x:v>
@@ -30324,7 +30324,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F503" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G503" s="0" t="s">
         <x:v>10</x:v>
@@ -30416,7 +30416,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F507" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G507" s="0" t="s">
         <x:v>10</x:v>
@@ -30485,7 +30485,7 @@
         <x:v>339</x:v>
       </x:c>
       <x:c r="F510" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G510" s="0" t="s">
         <x:v>10</x:v>
@@ -30531,7 +30531,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F512" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G512" s="0" t="s">
         <x:v>10</x:v>
@@ -30577,7 +30577,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F514" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G514" s="0" t="s">
         <x:v>10</x:v>
@@ -30600,7 +30600,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F515" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G515" s="0" t="s">
         <x:v>10</x:v>
@@ -30692,7 +30692,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F519" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G519" s="0" t="s">
         <x:v>10</x:v>
@@ -30715,7 +30715,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F520" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G520" s="0" t="s">
         <x:v>10</x:v>
@@ -30784,7 +30784,7 @@
         <x:v>339</x:v>
       </x:c>
       <x:c r="F523" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G523" s="0" t="s">
         <x:v>10</x:v>
@@ -30807,7 +30807,7 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="F524" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G524" s="0" t="s">
         <x:v>10</x:v>
@@ -30991,7 +30991,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F532" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G532" s="0" t="s">
         <x:v>10</x:v>
@@ -31014,7 +31014,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F533" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G533" s="0" t="s">
         <x:v>10</x:v>
@@ -31037,7 +31037,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F534" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G534" s="0" t="s">
         <x:v>10</x:v>
@@ -31129,7 +31129,7 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="F538" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G538" s="0" t="s">
         <x:v>10</x:v>
@@ -31152,7 +31152,7 @@
         <x:v>192</x:v>
       </x:c>
       <x:c r="F539" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G539" s="0" t="s">
         <x:v>10</x:v>
@@ -31244,7 +31244,7 @@
         <x:v>231</x:v>
       </x:c>
       <x:c r="F543" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G543" s="0" t="s">
         <x:v>10</x:v>
@@ -31428,7 +31428,7 @@
         <x:v>343</x:v>
       </x:c>
       <x:c r="F551" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G551" s="0" t="s">
         <x:v>10</x:v>
@@ -31451,7 +31451,7 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="F552" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G552" s="0" t="s">
         <x:v>10</x:v>
@@ -31612,7 +31612,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F559" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G559" s="0" t="s">
         <x:v>10</x:v>
@@ -31681,7 +31681,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F562" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G562" s="0" t="s">
         <x:v>10</x:v>
@@ -31704,7 +31704,7 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="F563" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G563" s="0" t="s">
         <x:v>10</x:v>
@@ -31773,7 +31773,7 @@
         <x:v>339</x:v>
       </x:c>
       <x:c r="F566" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G566" s="0" t="s">
         <x:v>10</x:v>
@@ -31819,7 +31819,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F568" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G568" s="0" t="s">
         <x:v>10</x:v>
@@ -31865,7 +31865,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F570" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G570" s="0" t="s">
         <x:v>10</x:v>
@@ -31888,7 +31888,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F571" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G571" s="0" t="s">
         <x:v>10</x:v>
@@ -31934,7 +31934,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F573" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G573" s="0" t="s">
         <x:v>10</x:v>
@@ -32026,7 +32026,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F577" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G577" s="0" t="s">
         <x:v>10</x:v>
@@ -32049,7 +32049,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F578" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G578" s="0" t="s">
         <x:v>10</x:v>
@@ -32072,7 +32072,7 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="F579" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G579" s="0" t="s">
         <x:v>10</x:v>
@@ -32095,7 +32095,7 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="F580" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G580" s="0" t="s">
         <x:v>10</x:v>
@@ -32164,7 +32164,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F583" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G583" s="0" t="s">
         <x:v>10</x:v>
@@ -32256,7 +32256,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F587" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G587" s="0" t="s">
         <x:v>10</x:v>
@@ -32302,7 +32302,7 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="F589" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G589" s="0" t="s">
         <x:v>10</x:v>
@@ -32555,7 +32555,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F600" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G600" s="0" t="s">
         <x:v>10</x:v>
@@ -32716,7 +32716,7 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="F607" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G607" s="0" t="s">
         <x:v>10</x:v>
@@ -32785,7 +32785,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F610" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G610" s="0" t="s">
         <x:v>10</x:v>
@@ -32808,7 +32808,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F611" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G611" s="0" t="s">
         <x:v>10</x:v>
@@ -32831,7 +32831,7 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="F612" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G612" s="0" t="s">
         <x:v>10</x:v>
@@ -32900,7 +32900,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F615" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G615" s="0" t="s">
         <x:v>10</x:v>
@@ -32923,7 +32923,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F616" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G616" s="0" t="s">
         <x:v>10</x:v>
@@ -32992,7 +32992,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F619" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G619" s="0" t="s">
         <x:v>10</x:v>
@@ -33199,7 +33199,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F628" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G628" s="0" t="s">
         <x:v>10</x:v>
@@ -33314,7 +33314,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F633" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G633" s="0" t="s">
         <x:v>10</x:v>
@@ -33337,7 +33337,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F634" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G634" s="0" t="s">
         <x:v>10</x:v>
@@ -33406,7 +33406,7 @@
         <x:v>192</x:v>
       </x:c>
       <x:c r="F637" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G637" s="0" t="s">
         <x:v>10</x:v>
@@ -33659,7 +33659,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F648" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G648" s="0" t="s">
         <x:v>10</x:v>
@@ -33682,7 +33682,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F649" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G649" s="0" t="s">
         <x:v>10</x:v>
@@ -33728,7 +33728,7 @@
         <x:v>339</x:v>
       </x:c>
       <x:c r="F651" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G651" s="0" t="s">
         <x:v>10</x:v>
@@ -33751,7 +33751,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F652" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G652" s="0" t="s">
         <x:v>10</x:v>
@@ -33774,7 +33774,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F653" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G653" s="0" t="s">
         <x:v>10</x:v>
@@ -33889,7 +33889,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F658" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G658" s="0" t="s">
         <x:v>10</x:v>
@@ -33912,7 +33912,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F659" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G659" s="0" t="s">
         <x:v>10</x:v>
@@ -33958,7 +33958,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F661" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G661" s="0" t="s">
         <x:v>10</x:v>
@@ -33981,7 +33981,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F662" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G662" s="0" t="s">
         <x:v>10</x:v>
@@ -34004,7 +34004,7 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="F663" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G663" s="0" t="s">
         <x:v>10</x:v>
@@ -34234,7 +34234,7 @@
         <x:v>298</x:v>
       </x:c>
       <x:c r="F673" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G673" s="0" t="s">
         <x:v>10</x:v>
@@ -34349,7 +34349,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F678" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G678" s="0" t="s">
         <x:v>10</x:v>
@@ -35108,7 +35108,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F711" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G711" s="0" t="s">
         <x:v>10</x:v>
@@ -35131,7 +35131,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F712" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G712" s="0" t="s">
         <x:v>10</x:v>
@@ -35154,7 +35154,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F713" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G713" s="0" t="s">
         <x:v>10</x:v>
@@ -35223,7 +35223,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F716" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G716" s="0" t="s">
         <x:v>10</x:v>
@@ -35246,7 +35246,7 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="F717" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G717" s="0" t="s">
         <x:v>10</x:v>
@@ -35338,7 +35338,7 @@
         <x:v>339</x:v>
       </x:c>
       <x:c r="F721" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G721" s="0" t="s">
         <x:v>10</x:v>
@@ -35407,7 +35407,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F724" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G724" s="0" t="s">
         <x:v>10</x:v>
@@ -35430,7 +35430,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F725" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G725" s="0" t="s">
         <x:v>10</x:v>
@@ -35453,7 +35453,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F726" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G726" s="0" t="s">
         <x:v>10</x:v>
@@ -35706,7 +35706,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F737" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G737" s="0" t="s">
         <x:v>10</x:v>
@@ -35890,7 +35890,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F745" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G745" s="0" t="s">
         <x:v>10</x:v>
@@ -35936,7 +35936,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F747" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G747" s="0" t="s">
         <x:v>10</x:v>
@@ -35982,7 +35982,7 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="F749" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G749" s="0" t="s">
         <x:v>10</x:v>
@@ -36005,7 +36005,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F750" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G750" s="0" t="s">
         <x:v>10</x:v>
@@ -36028,7 +36028,7 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="F751" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G751" s="0" t="s">
         <x:v>10</x:v>
@@ -36189,7 +36189,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F758" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G758" s="0" t="s">
         <x:v>10</x:v>
@@ -36212,7 +36212,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F759" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G759" s="0" t="s">
         <x:v>10</x:v>
@@ -36235,7 +36235,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F760" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G760" s="0" t="s">
         <x:v>10</x:v>
@@ -36258,7 +36258,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F761" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G761" s="0" t="s">
         <x:v>10</x:v>
@@ -36350,7 +36350,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F765" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G765" s="0" t="s">
         <x:v>10</x:v>
@@ -36465,7 +36465,7 @@
         <x:v>298</x:v>
       </x:c>
       <x:c r="F770" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G770" s="0" t="s">
         <x:v>10</x:v>
@@ -36488,7 +36488,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F771" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G771" s="0" t="s">
         <x:v>10</x:v>
@@ -36672,7 +36672,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F779" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G779" s="0" t="s">
         <x:v>10</x:v>
@@ -36764,7 +36764,7 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="F783" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G783" s="0" t="s">
         <x:v>10</x:v>
@@ -36787,7 +36787,7 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="F784" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G784" s="0" t="s">
         <x:v>10</x:v>
@@ -36810,7 +36810,7 @@
         <x:v>192</x:v>
       </x:c>
       <x:c r="F785" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G785" s="0" t="s">
         <x:v>10</x:v>
@@ -36971,7 +36971,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F792" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G792" s="0" t="s">
         <x:v>10</x:v>
@@ -36994,7 +36994,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F793" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G793" s="0" t="s">
         <x:v>10</x:v>
@@ -37040,7 +37040,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F795" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G795" s="0" t="s">
         <x:v>10</x:v>
@@ -37086,7 +37086,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F797" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G797" s="0" t="s">
         <x:v>10</x:v>
@@ -37109,7 +37109,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F798" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G798" s="0" t="s">
         <x:v>10</x:v>
@@ -37132,7 +37132,7 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="F799" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G799" s="0" t="s">
         <x:v>10</x:v>
@@ -37201,7 +37201,7 @@
         <x:v>339</x:v>
       </x:c>
       <x:c r="F802" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G802" s="0" t="s">
         <x:v>10</x:v>
@@ -37293,7 +37293,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F806" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G806" s="0" t="s">
         <x:v>10</x:v>
@@ -37362,7 +37362,7 @@
         <x:v>339</x:v>
       </x:c>
       <x:c r="F809" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G809" s="0" t="s">
         <x:v>10</x:v>
@@ -37385,7 +37385,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F810" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G810" s="0" t="s">
         <x:v>10</x:v>
@@ -37408,7 +37408,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F811" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G811" s="0" t="s">
         <x:v>10</x:v>
@@ -37477,7 +37477,7 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="F814" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G814" s="0" t="s">
         <x:v>10</x:v>
@@ -37707,7 +37707,7 @@
         <x:v>339</x:v>
       </x:c>
       <x:c r="F824" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G824" s="0" t="s">
         <x:v>10</x:v>
@@ -37730,7 +37730,7 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="F825" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G825" s="0" t="s">
         <x:v>10</x:v>
@@ -37845,7 +37845,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F830" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G830" s="0" t="s">
         <x:v>10</x:v>
@@ -38006,7 +38006,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F837" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G837" s="0" t="s">
         <x:v>10</x:v>
@@ -38052,7 +38052,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F839" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G839" s="0" t="s">
         <x:v>10</x:v>
@@ -38236,7 +38236,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F847" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G847" s="0" t="s">
         <x:v>10</x:v>
@@ -38259,7 +38259,7 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="F848" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G848" s="0" t="s">
         <x:v>10</x:v>
@@ -38328,7 +38328,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F851" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G851" s="0" t="s">
         <x:v>10</x:v>
@@ -38351,7 +38351,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F852" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G852" s="0" t="s">
         <x:v>10</x:v>
@@ -38420,7 +38420,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F855" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G855" s="0" t="s">
         <x:v>10</x:v>
@@ -38443,7 +38443,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F856" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G856" s="0" t="s">
         <x:v>10</x:v>
@@ -38466,7 +38466,7 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="F857" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G857" s="0" t="s">
         <x:v>10</x:v>
@@ -38558,7 +38558,7 @@
         <x:v>339</x:v>
       </x:c>
       <x:c r="F861" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G861" s="0" t="s">
         <x:v>10</x:v>
@@ -38581,7 +38581,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F862" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G862" s="0" t="s">
         <x:v>10</x:v>
@@ -38650,7 +38650,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F865" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G865" s="0" t="s">
         <x:v>10</x:v>
@@ -38742,7 +38742,7 @@
         <x:v>298</x:v>
       </x:c>
       <x:c r="F869" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G869" s="0" t="s">
         <x:v>10</x:v>
@@ -38811,7 +38811,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F872" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G872" s="0" t="s">
         <x:v>10</x:v>
@@ -38834,7 +38834,7 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="F873" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G873" s="0" t="s">
         <x:v>10</x:v>
@@ -39110,7 +39110,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F885" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G885" s="0" t="s">
         <x:v>10</x:v>
@@ -39225,7 +39225,7 @@
         <x:v>231</x:v>
       </x:c>
       <x:c r="F890" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G890" s="0" t="s">
         <x:v>10</x:v>
@@ -39593,7 +39593,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F906" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G906" s="0" t="s">
         <x:v>10</x:v>
@@ -39892,7 +39892,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F919" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G919" s="0" t="s">
         <x:v>10</x:v>
@@ -40145,7 +40145,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F930" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G930" s="0" t="s">
         <x:v>10</x:v>
@@ -40237,7 +40237,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F934" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G934" s="0" t="s">
         <x:v>10</x:v>
@@ -40283,7 +40283,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F936" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G936" s="0" t="s">
         <x:v>10</x:v>
@@ -40398,7 +40398,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F941" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G941" s="0" t="s">
         <x:v>10</x:v>
@@ -40536,7 +40536,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F947" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G947" s="0" t="s">
         <x:v>10</x:v>
@@ -40720,7 +40720,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F955" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G955" s="0" t="s">
         <x:v>10</x:v>
@@ -40789,7 +40789,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F958" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G958" s="0" t="s">
         <x:v>10</x:v>
@@ -40812,7 +40812,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F959" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G959" s="0" t="s">
         <x:v>10</x:v>
@@ -40835,7 +40835,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F960" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G960" s="0" t="s">
         <x:v>10</x:v>
@@ -40858,7 +40858,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F961" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G961" s="0" t="s">
         <x:v>10</x:v>
@@ -40881,7 +40881,7 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="F962" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G962" s="0" t="s">
         <x:v>10</x:v>
@@ -40973,7 +40973,7 @@
         <x:v>339</x:v>
       </x:c>
       <x:c r="F966" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G966" s="0" t="s">
         <x:v>10</x:v>
@@ -41065,7 +41065,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F970" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G970" s="0" t="s">
         <x:v>10</x:v>
@@ -41203,7 +41203,7 @@
         <x:v>231</x:v>
       </x:c>
       <x:c r="F976" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G976" s="0" t="s">
         <x:v>10</x:v>
@@ -41410,7 +41410,7 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="F985" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G985" s="0" t="s">
         <x:v>10</x:v>
@@ -41594,7 +41594,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F993" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G993" s="0" t="s">
         <x:v>10</x:v>
@@ -41617,7 +41617,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F994" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G994" s="0" t="s">
         <x:v>10</x:v>
@@ -41709,7 +41709,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F998" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G998" s="0" t="s">
         <x:v>10</x:v>
@@ -41732,7 +41732,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F999" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G999" s="0" t="s">
         <x:v>10</x:v>
@@ -41778,7 +41778,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F1001" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1001" s="0" t="s">
         <x:v>10</x:v>
@@ -41801,7 +41801,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F1002" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1002" s="0" t="s">
         <x:v>10</x:v>
@@ -41847,7 +41847,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F1004" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G1004" s="0" t="s">
         <x:v>10</x:v>
@@ -41870,7 +41870,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F1005" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1005" s="0" t="s">
         <x:v>10</x:v>
@@ -41939,7 +41939,7 @@
         <x:v>339</x:v>
       </x:c>
       <x:c r="F1008" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G1008" s="0" t="s">
         <x:v>10</x:v>
@@ -42008,7 +42008,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F1011" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1011" s="0" t="s">
         <x:v>10</x:v>
@@ -42054,7 +42054,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F1013" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G1013" s="0" t="s">
         <x:v>10</x:v>
@@ -42077,7 +42077,7 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="F1014" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G1014" s="0" t="s">
         <x:v>10</x:v>
@@ -42123,7 +42123,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F1016" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1016" s="0" t="s">
         <x:v>10</x:v>
@@ -42261,7 +42261,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F1022" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1022" s="0" t="s">
         <x:v>10</x:v>
@@ -42330,7 +42330,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F1025" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G1025" s="0" t="s">
         <x:v>10</x:v>
@@ -42399,7 +42399,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F1028" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G1028" s="0" t="s">
         <x:v>10</x:v>
@@ -42422,7 +42422,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F1029" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G1029" s="0" t="s">
         <x:v>10</x:v>
@@ -42445,7 +42445,7 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="F1030" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G1030" s="0" t="s">
         <x:v>10</x:v>
@@ -42514,7 +42514,7 @@
         <x:v>339</x:v>
       </x:c>
       <x:c r="F1033" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G1033" s="0" t="s">
         <x:v>10</x:v>
@@ -42560,7 +42560,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F1035" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G1035" s="0" t="s">
         <x:v>10</x:v>
@@ -42652,7 +42652,7 @@
         <x:v>298</x:v>
       </x:c>
       <x:c r="F1039" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1039" s="0" t="s">
         <x:v>10</x:v>
@@ -42698,7 +42698,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F1041" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G1041" s="0" t="s">
         <x:v>10</x:v>
@@ -42721,7 +42721,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F1042" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G1042" s="0" t="s">
         <x:v>10</x:v>
@@ -42790,7 +42790,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F1045" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1045" s="0" t="s">
         <x:v>10</x:v>
@@ -42813,7 +42813,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F1046" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G1046" s="0" t="s">
         <x:v>10</x:v>
@@ -42836,7 +42836,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F1047" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1047" s="0" t="s">
         <x:v>10</x:v>
@@ -42859,7 +42859,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F1048" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G1048" s="0" t="s">
         <x:v>10</x:v>
@@ -42974,7 +42974,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F1053" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1053" s="0" t="s">
         <x:v>10</x:v>
@@ -42997,7 +42997,7 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="F1054" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G1054" s="0" t="s">
         <x:v>10</x:v>
@@ -43020,7 +43020,7 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="F1055" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1055" s="0" t="s">
         <x:v>10</x:v>
@@ -43043,7 +43043,7 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="F1056" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G1056" s="0" t="s">
         <x:v>10</x:v>
@@ -43227,7 +43227,7 @@
         <x:v>339</x:v>
       </x:c>
       <x:c r="F1064" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G1064" s="0" t="s">
         <x:v>10</x:v>
@@ -43273,7 +43273,7 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="F1066" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1066" s="0" t="s">
         <x:v>10</x:v>
@@ -43457,7 +43457,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F1074" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G1074" s="0" t="s">
         <x:v>10</x:v>
@@ -43480,7 +43480,7 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="F1075" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G1075" s="0" t="s">
         <x:v>10</x:v>
@@ -43549,7 +43549,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F1078" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G1078" s="0" t="s">
         <x:v>10</x:v>
@@ -43710,7 +43710,7 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="F1085" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1085" s="0" t="s">
         <x:v>10</x:v>
@@ -44101,7 +44101,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F1102" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G1102" s="0" t="s">
         <x:v>10</x:v>
@@ -44124,7 +44124,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F1103" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G1103" s="0" t="s">
         <x:v>10</x:v>
@@ -44170,7 +44170,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F1105" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1105" s="0" t="s">
         <x:v>10</x:v>
@@ -44262,7 +44262,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F1109" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1109" s="0" t="s">
         <x:v>10</x:v>
@@ -44400,7 +44400,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F1115" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1115" s="0" t="s">
         <x:v>10</x:v>
@@ -44492,7 +44492,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F1119" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G1119" s="0" t="s">
         <x:v>10</x:v>
@@ -44515,7 +44515,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F1120" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1120" s="0" t="s">
         <x:v>10</x:v>
@@ -44607,7 +44607,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F1124" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G1124" s="0" t="s">
         <x:v>10</x:v>
@@ -44630,7 +44630,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F1125" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G1125" s="0" t="s">
         <x:v>10</x:v>
@@ -44653,7 +44653,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F1126" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1126" s="0" t="s">
         <x:v>10</x:v>
@@ -44676,7 +44676,7 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="F1127" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G1127" s="0" t="s">
         <x:v>10</x:v>
@@ -44768,7 +44768,7 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="F1131" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G1131" s="0" t="s">
         <x:v>10</x:v>
@@ -44791,7 +44791,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F1132" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1132" s="0" t="s">
         <x:v>10</x:v>
@@ -44814,7 +44814,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F1133" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G1133" s="0" t="s">
         <x:v>10</x:v>
@@ -44837,7 +44837,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F1134" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1134" s="0" t="s">
         <x:v>10</x:v>
@@ -44860,7 +44860,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F1135" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G1135" s="0" t="s">
         <x:v>10</x:v>
@@ -44906,7 +44906,7 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="F1137" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1137" s="0" t="s">
         <x:v>10</x:v>
@@ -44998,7 +44998,7 @@
         <x:v>339</x:v>
       </x:c>
       <x:c r="F1141" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G1141" s="0" t="s">
         <x:v>10</x:v>
@@ -45044,7 +45044,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F1143" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1143" s="0" t="s">
         <x:v>10</x:v>
@@ -45090,7 +45090,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F1145" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1145" s="0" t="s">
         <x:v>10</x:v>
@@ -45113,7 +45113,7 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="F1146" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G1146" s="0" t="s">
         <x:v>10</x:v>
@@ -45228,7 +45228,7 @@
         <x:v>343</x:v>
       </x:c>
       <x:c r="F1151" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G1151" s="0" t="s">
         <x:v>10</x:v>
@@ -45251,7 +45251,7 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="F1152" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1152" s="0" t="s">
         <x:v>10</x:v>
@@ -45297,7 +45297,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F1154" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G1154" s="0" t="s">
         <x:v>10</x:v>
@@ -45320,7 +45320,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F1155" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1155" s="0" t="s">
         <x:v>10</x:v>
@@ -45389,7 +45389,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F1158" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G1158" s="0" t="s">
         <x:v>10</x:v>
@@ -45412,7 +45412,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F1159" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1159" s="0" t="s">
         <x:v>10</x:v>
@@ -45481,7 +45481,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F1162" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1162" s="0" t="s">
         <x:v>10</x:v>
@@ -45504,7 +45504,7 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="F1163" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G1163" s="0" t="s">
         <x:v>10</x:v>
@@ -45596,7 +45596,7 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="F1167" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G1167" s="0" t="s">
         <x:v>10</x:v>
@@ -45734,7 +45734,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F1173" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1173" s="0" t="s">
         <x:v>10</x:v>
@@ -46056,7 +46056,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F1187" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1187" s="0" t="s">
         <x:v>10</x:v>
@@ -46125,7 +46125,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F1190" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G1190" s="0" t="s">
         <x:v>10</x:v>
@@ -46263,7 +46263,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F1196" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G1196" s="0" t="s">
         <x:v>10</x:v>
@@ -46286,7 +46286,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F1197" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1197" s="0" t="s">
         <x:v>10</x:v>
@@ -46378,7 +46378,7 @@
         <x:v>339</x:v>
       </x:c>
       <x:c r="F1201" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G1201" s="0" t="s">
         <x:v>10</x:v>
@@ -46470,7 +46470,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F1205" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1205" s="0" t="s">
         <x:v>10</x:v>
@@ -46493,7 +46493,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F1206" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G1206" s="0" t="s">
         <x:v>10</x:v>
@@ -46516,7 +46516,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F1207" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1207" s="0" t="s">
         <x:v>10</x:v>
@@ -46585,7 +46585,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F1210" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G1210" s="0" t="s">
         <x:v>10</x:v>
@@ -46608,7 +46608,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F1211" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1211" s="0" t="s">
         <x:v>10</x:v>
@@ -46631,7 +46631,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F1212" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G1212" s="0" t="s">
         <x:v>10</x:v>
@@ -46723,7 +46723,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F1216" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G1216" s="0" t="s">
         <x:v>10</x:v>
@@ -46746,7 +46746,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F1217" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1217" s="0" t="s">
         <x:v>10</x:v>
@@ -46769,7 +46769,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F1218" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1218" s="0" t="s">
         <x:v>10</x:v>
@@ -46792,7 +46792,7 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="F1219" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G1219" s="0" t="s">
         <x:v>10</x:v>
@@ -46838,7 +46838,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F1221" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1221" s="0" t="s">
         <x:v>10</x:v>
@@ -46861,7 +46861,7 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="F1222" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G1222" s="0" t="s">
         <x:v>10</x:v>
@@ -46976,7 +46976,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F1227" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1227" s="0" t="s">
         <x:v>10</x:v>
@@ -47068,7 +47068,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F1231" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1231" s="0" t="s">
         <x:v>10</x:v>
@@ -47160,7 +47160,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F1235" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G1235" s="0" t="s">
         <x:v>10</x:v>
@@ -47183,7 +47183,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F1236" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1236" s="0" t="s">
         <x:v>10</x:v>
@@ -47252,7 +47252,7 @@
         <x:v>192</x:v>
       </x:c>
       <x:c r="F1239" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1239" s="0" t="s">
         <x:v>10</x:v>
@@ -47919,7 +47919,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F1268" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G1268" s="0" t="s">
         <x:v>10</x:v>
@@ -47942,7 +47942,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F1269" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1269" s="0" t="s">
         <x:v>10</x:v>
@@ -48172,7 +48172,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F1279" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1279" s="0" t="s">
         <x:v>10</x:v>
@@ -48218,7 +48218,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F1281" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1281" s="0" t="s">
         <x:v>10</x:v>
@@ -48471,7 +48471,7 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="F1292" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G1292" s="0" t="s">
         <x:v>10</x:v>
@@ -48494,7 +48494,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F1293" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G1293" s="0" t="s">
         <x:v>10</x:v>
@@ -48678,7 +48678,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F1301" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G1301" s="0" t="s">
         <x:v>10</x:v>
@@ -48701,7 +48701,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F1302" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1302" s="0" t="s">
         <x:v>10</x:v>
@@ -48770,7 +48770,7 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="F1305" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G1305" s="0" t="s">
         <x:v>10</x:v>
@@ -48793,7 +48793,7 @@
         <x:v>232</x:v>
       </x:c>
       <x:c r="F1306" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1306" s="0" t="s">
         <x:v>10</x:v>
@@ -48839,7 +48839,7 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="F1308" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1308" s="0" t="s">
         <x:v>10</x:v>
@@ -48931,7 +48931,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F1312" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1312" s="0" t="s">
         <x:v>10</x:v>
@@ -48977,7 +48977,7 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="F1314" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1314" s="0" t="s">
         <x:v>10</x:v>
@@ -49092,7 +49092,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F1319" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1319" s="0" t="s">
         <x:v>10</x:v>
@@ -49115,7 +49115,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F1320" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1320" s="0" t="s">
         <x:v>10</x:v>
@@ -49230,7 +49230,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F1325" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G1325" s="0" t="s">
         <x:v>10</x:v>
@@ -49253,7 +49253,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F1326" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1326" s="0" t="s">
         <x:v>10</x:v>
@@ -49276,7 +49276,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F1327" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G1327" s="0" t="s">
         <x:v>10</x:v>
@@ -49345,7 +49345,7 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="F1330" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1330" s="0" t="s">
         <x:v>10</x:v>
@@ -49368,7 +49368,7 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="F1331" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G1331" s="0" t="s">
         <x:v>10</x:v>
@@ -49851,7 +49851,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F1352" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1352" s="0" t="s">
         <x:v>10</x:v>
@@ -49897,7 +49897,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F1354" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G1354" s="0" t="s">
         <x:v>10</x:v>
@@ -49920,7 +49920,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F1355" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1355" s="0" t="s">
         <x:v>10</x:v>
@@ -50012,7 +50012,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F1359" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1359" s="0" t="s">
         <x:v>10</x:v>
@@ -50081,7 +50081,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F1362" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1362" s="0" t="s">
         <x:v>10</x:v>
@@ -50127,7 +50127,7 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="F1364" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G1364" s="0" t="s">
         <x:v>10</x:v>
@@ -50196,7 +50196,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F1367" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1367" s="0" t="s">
         <x:v>10</x:v>
@@ -50265,7 +50265,7 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="F1370" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1370" s="0" t="s">
         <x:v>10</x:v>
@@ -50288,7 +50288,7 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="F1371" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G1371" s="0" t="s">
         <x:v>10</x:v>
@@ -50311,7 +50311,7 @@
         <x:v>232</x:v>
       </x:c>
       <x:c r="F1372" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1372" s="0" t="s">
         <x:v>10</x:v>
@@ -50426,7 +50426,7 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="F1377" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1377" s="0" t="s">
         <x:v>10</x:v>
@@ -50587,7 +50587,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F1384" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1384" s="0" t="s">
         <x:v>10</x:v>
@@ -50702,7 +50702,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F1389" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1389" s="0" t="s">
         <x:v>10</x:v>
@@ -50725,7 +50725,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F1390" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1390" s="0" t="s">
         <x:v>10</x:v>
@@ -50817,7 +50817,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F1394" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1394" s="0" t="s">
         <x:v>10</x:v>
@@ -50886,7 +50886,7 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="F1397" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1397" s="0" t="s">
         <x:v>10</x:v>
@@ -50932,7 +50932,7 @@
         <x:v>298</x:v>
       </x:c>
       <x:c r="F1399" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1399" s="0" t="s">
         <x:v>10</x:v>
@@ -51024,7 +51024,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F1403" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1403" s="0" t="s">
         <x:v>10</x:v>
@@ -51093,7 +51093,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="F1406" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1406" s="0" t="s">
         <x:v>10</x:v>
@@ -51116,7 +51116,7 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="F1407" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G1407" s="0" t="s">
         <x:v>10</x:v>
@@ -51139,7 +51139,7 @@
         <x:v>231</x:v>
       </x:c>
       <x:c r="F1408" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1408" s="0" t="s">
         <x:v>10</x:v>
@@ -51208,7 +51208,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F1411" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G1411" s="0" t="s">
         <x:v>10</x:v>
@@ -51231,7 +51231,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F1412" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1412" s="0" t="s">
         <x:v>10</x:v>
@@ -51300,7 +51300,7 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="F1415" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G1415" s="0" t="s">
         <x:v>10</x:v>
@@ -51323,7 +51323,7 @@
         <x:v>192</x:v>
       </x:c>
       <x:c r="F1416" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1416" s="0" t="s">
         <x:v>10</x:v>
@@ -51346,7 +51346,7 @@
         <x:v>231</x:v>
       </x:c>
       <x:c r="F1417" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G1417" s="0" t="s">
         <x:v>10</x:v>

--- a/reports/pro-crypto/pro-crypto-bundler-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-bundler-report.xlsx
@@ -152,27 +152,27 @@
     <x:t>ANDERSON</x:t>
   </x:si>
   <x:si>
+    <x:t>C00824896</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLOCKCHAIN ASSOCIATION POLITICAL ACTION COMMITTEE (BA PAC)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANDREESSEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LOS ALTOS</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00821082</x:t>
   </x:si>
   <x:si>
     <x:t>DIGITAL FUTURE PAC</x:t>
   </x:si>
   <x:si>
-    <x:t>MARC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANDREESSEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LOS ALTOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00824896</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLOCKCHAIN ASSOCIATION POLITICAL ACTION COMMITTEE (BA PAC)</x:t>
-  </x:si>
-  <x:si>
     <x:t>C00852657</x:t>
   </x:si>
   <x:si>
@@ -2141,7 +2141,7 @@
     <x:t>DIGITAL FUTURE PAC,BLOCKCHAIN ASSOCIATION POLITICAL ACTION COMMITTEE (BA PAC)</x:t>
   </x:si>
   <x:si>
-    <x:t>STAND WITH CRYPTO ALLIANCE, INC. POLITICAL ACTION COMMITTEE,FAIRSHAKE</x:t>
+    <x:t>FAIRSHAKE,STAND WITH CRYPTO ALLIANCE, INC. POLITICAL ACTION COMMITTEE</x:t>
   </x:si>
   <x:si>
     <x:t>lobby_total</x:t>
@@ -6063,7 +6063,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="G12" s="1">
-        <x:v>5000</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
@@ -6086,7 +6086,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="G13" s="1">
-        <x:v>10000</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
@@ -6109,7 +6109,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="G14" s="1">
-        <x:v>15000</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
@@ -6183,10 +6183,10 @@
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>59</x:v>
@@ -6201,15 +6201,15 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="G18" s="1">
-        <x:v>15000</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>59</x:v>
@@ -6224,7 +6224,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="G19" s="1">
-        <x:v>5000</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
@@ -6747,13 +6747,13 @@
         <x:v>119</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F42" s="1" t="s">
         <x:v>68</x:v>
       </x:c>
       <x:c r="G42" s="1">
-        <x:v>1000</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7">
@@ -6770,13 +6770,13 @@
         <x:v>119</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="F43" s="1" t="s">
         <x:v>68</x:v>
       </x:c>
       <x:c r="G43" s="1">
-        <x:v>5000</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7">
@@ -8041,15 +8041,15 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="G98" s="1">
-        <x:v>15000</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:7">
       <x:c r="A99" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B99" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
         <x:v>250</x:v>
@@ -8069,10 +8069,10 @@
     </x:row>
     <x:row r="100" spans="1:7">
       <x:c r="A100" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B100" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
         <x:v>250</x:v>
@@ -8092,10 +8092,10 @@
     </x:row>
     <x:row r="101" spans="1:7">
       <x:c r="A101" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B101" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
         <x:v>250</x:v>
@@ -9449,10 +9449,10 @@
     </x:row>
     <x:row r="160" spans="1:7">
       <x:c r="A160" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B160" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C160" s="1" t="s">
         <x:v>108</x:v>
@@ -9536,15 +9536,15 @@
         <x:v>369</x:v>
       </x:c>
       <x:c r="G163" s="1">
-        <x:v>15000</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:7">
       <x:c r="A164" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B164" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C164" s="1" t="s">
         <x:v>271</x:v>
@@ -9564,10 +9564,10 @@
     </x:row>
     <x:row r="165" spans="1:7">
       <x:c r="A165" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B165" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C165" s="1" t="s">
         <x:v>129</x:v>
@@ -9587,10 +9587,10 @@
     </x:row>
     <x:row r="166" spans="1:7">
       <x:c r="A166" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B166" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C166" s="1" t="s">
         <x:v>370</x:v>
@@ -9628,7 +9628,7 @@
         <x:v>369</x:v>
       </x:c>
       <x:c r="G167" s="1">
-        <x:v>15000</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="168" spans="1:7">
@@ -9748,10 +9748,10 @@
     </x:row>
     <x:row r="173" spans="1:7">
       <x:c r="A173" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B173" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C173" s="1" t="s">
         <x:v>382</x:v>
@@ -9817,10 +9817,10 @@
     </x:row>
     <x:row r="176" spans="1:7">
       <x:c r="A176" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B176" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C176" s="1" t="s">
         <x:v>388</x:v>
@@ -10070,10 +10070,10 @@
     </x:row>
     <x:row r="187" spans="1:7">
       <x:c r="A187" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B187" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C187" s="1" t="s">
         <x:v>409</x:v>
@@ -10599,10 +10599,10 @@
     </x:row>
     <x:row r="210" spans="1:7">
       <x:c r="A210" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B210" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C210" s="1" t="s">
         <x:v>453</x:v>
@@ -10795,13 +10795,13 @@
         <x:v>467</x:v>
       </x:c>
       <x:c r="E218" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F218" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G218" s="1">
-        <x:v>20000</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="219" spans="1:7">
@@ -10818,13 +10818,13 @@
         <x:v>467</x:v>
       </x:c>
       <x:c r="E219" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F219" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G219" s="1">
-        <x:v>2000</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="220" spans="1:7">
@@ -11059,10 +11059,10 @@
     </x:row>
     <x:row r="230" spans="1:7">
       <x:c r="A230" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B230" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C230" s="1" t="s">
         <x:v>485</x:v>
@@ -11289,10 +11289,10 @@
     </x:row>
     <x:row r="240" spans="1:7">
       <x:c r="A240" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B240" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C240" s="1" t="s">
         <x:v>439</x:v>
@@ -12301,10 +12301,10 @@
     </x:row>
     <x:row r="284" spans="1:7">
       <x:c r="A284" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B284" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C284" s="1" t="s">
         <x:v>579</x:v>
@@ -12370,10 +12370,10 @@
     </x:row>
     <x:row r="287" spans="1:7">
       <x:c r="A287" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B287" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C287" s="1" t="s">
         <x:v>585</x:v>
@@ -12710,7 +12710,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="G301" s="1">
-        <x:v>15000</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="302" spans="1:7">
@@ -12784,10 +12784,10 @@
     </x:row>
     <x:row r="305" spans="1:7">
       <x:c r="A305" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B305" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C305" s="1" t="s">
         <x:v>613</x:v>
@@ -12853,10 +12853,10 @@
     </x:row>
     <x:row r="308" spans="1:7">
       <x:c r="A308" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B308" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C308" s="1" t="s">
         <x:v>616</x:v>
@@ -12945,10 +12945,10 @@
     </x:row>
     <x:row r="312" spans="1:7">
       <x:c r="A312" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B312" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C312" s="1" t="s">
         <x:v>626</x:v>
@@ -13980,10 +13980,10 @@
     </x:row>
     <x:row r="357" spans="1:7">
       <x:c r="A357" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B357" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C357" s="1" t="s">
         <x:v>331</x:v>
@@ -14441,7 +14441,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="E14" s="1">
-        <x:v>30000</x:v>
+        <x:v>35000</x:v>
       </x:c>
       <x:c r="F14" s="2" t="s">
         <x:v>702</x:v>
@@ -14449,27 +14449,27 @@
     </x:row>
     <x:row r="15" spans="1:6">
       <x:c r="A15" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>324</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="E15" s="1">
-        <x:v>25000</x:v>
+        <x:v>30000</x:v>
       </x:c>
       <x:c r="F15" s="2" t="s">
-        <x:v>57</x:v>
+        <x:v>703</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:6">
       <x:c r="A16" s="1" t="s">
-        <x:v>271</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
         <x:v>367</x:v>
@@ -14484,75 +14484,75 @@
         <x:v>25000</x:v>
       </x:c>
       <x:c r="F16" s="2" t="s">
-        <x:v>703</x:v>
+        <x:v>704</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:6">
       <x:c r="A17" s="1" t="s">
-        <x:v>549</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>550</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>551</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E17" s="1">
         <x:v>25000</x:v>
       </x:c>
       <x:c r="F17" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>704</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:6">
       <x:c r="A18" s="1" t="s">
-        <x:v>347</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>348</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="E18" s="1">
-        <x:v>22066</x:v>
+        <x:v>25000</x:v>
       </x:c>
       <x:c r="F18" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:6">
       <x:c r="A19" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E19" s="1">
-        <x:v>21859</x:v>
+        <x:v>25000</x:v>
       </x:c>
       <x:c r="F19" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:6">
       <x:c r="A20" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>699</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>11</x:v>
@@ -14561,7 +14561,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="E20" s="1">
-        <x:v>20740</x:v>
+        <x:v>22066</x:v>
       </x:c>
       <x:c r="F20" s="2" t="s">
         <x:v>8</x:v>
@@ -14569,70 +14569,70 @@
     </x:row>
     <x:row r="21" spans="1:6">
       <x:c r="A21" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="E21" s="1">
-        <x:v>20000</x:v>
+        <x:v>21859</x:v>
       </x:c>
       <x:c r="F21" s="2" t="s">
-        <x:v>703</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:6">
       <x:c r="A22" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>467</x:v>
+        <x:v>699</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E22" s="1">
-        <x:v>20000</x:v>
+        <x:v>20740</x:v>
       </x:c>
       <x:c r="F22" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:6">
       <x:c r="A23" s="1" t="s">
-        <x:v>156</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>157</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E23" s="1">
         <x:v>20000</x:v>
       </x:c>
       <x:c r="F23" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:6">
       <x:c r="A24" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>11</x:v>
@@ -14649,42 +14649,42 @@
     </x:row>
     <x:row r="25" spans="1:6">
       <x:c r="A25" s="1" t="s">
-        <x:v>296</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>298</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>299</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>174</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E25" s="1">
         <x:v>20000</x:v>
       </x:c>
       <x:c r="F25" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:6">
       <x:c r="A26" s="1" t="s">
-        <x:v>370</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>367</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>368</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>369</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E26" s="1">
         <x:v>20000</x:v>
       </x:c>
       <x:c r="F26" s="2" t="s">
-        <x:v>704</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:6">
@@ -14709,16 +14709,16 @@
     </x:row>
     <x:row r="28" spans="1:6">
       <x:c r="A28" s="1" t="s">
-        <x:v>637</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>638</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>639</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="E28" s="1">
         <x:v>20000</x:v>
@@ -14729,130 +14729,130 @@
     </x:row>
     <x:row r="29" spans="1:6">
       <x:c r="A29" s="1" t="s">
-        <x:v>654</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>655</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="E29" s="1">
-        <x:v>19500</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="F29" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:6">
       <x:c r="A30" s="1" t="s">
-        <x:v>572</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>569</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="E30" s="1">
-        <x:v>19423</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="F30" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:6">
       <x:c r="A31" s="1" t="s">
-        <x:v>197</x:v>
+        <x:v>654</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>198</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="E31" s="1">
-        <x:v>18942</x:v>
+        <x:v>19500</x:v>
       </x:c>
       <x:c r="F31" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:6">
       <x:c r="A32" s="1" t="s">
-        <x:v>462</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>463</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>375</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E32" s="1">
-        <x:v>18000</x:v>
+        <x:v>19423</x:v>
       </x:c>
       <x:c r="F32" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:6">
       <x:c r="A33" s="1" t="s">
-        <x:v>405</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>406</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="E33" s="1">
-        <x:v>17933</x:v>
+        <x:v>18942</x:v>
       </x:c>
       <x:c r="F33" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:6">
       <x:c r="A34" s="1" t="s">
-        <x:v>341</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E34" s="1">
-        <x:v>15705</x:v>
+        <x:v>18000</x:v>
       </x:c>
       <x:c r="F34" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:6">
       <x:c r="A35" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
         <x:v>40</x:v>
@@ -14861,7 +14861,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="E35" s="1">
-        <x:v>15000</x:v>
+        <x:v>17933</x:v>
       </x:c>
       <x:c r="F35" s="2" t="s">
         <x:v>21</x:v>
@@ -14869,33 +14869,33 @@
     </x:row>
     <x:row r="36" spans="1:6">
       <x:c r="A36" s="1" t="s">
-        <x:v>510</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>511</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="E36" s="1">
-        <x:v>15000</x:v>
+        <x:v>15705</x:v>
       </x:c>
       <x:c r="F36" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:6">
       <x:c r="A37" s="1" t="s">
-        <x:v>456</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>457</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
         <x:v>12</x:v>
@@ -14904,15 +14904,15 @@
         <x:v>15000</x:v>
       </x:c>
       <x:c r="F37" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:6">
       <x:c r="A38" s="1" t="s">
-        <x:v>456</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>537</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
         <x:v>40</x:v>
@@ -14929,33 +14929,33 @@
     </x:row>
     <x:row r="39" spans="1:6">
       <x:c r="A39" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E39" s="1">
         <x:v>15000</x:v>
       </x:c>
       <x:c r="F39" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:6">
       <x:c r="A40" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>649</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
         <x:v>12</x:v>
@@ -14964,38 +14964,38 @@
         <x:v>15000</x:v>
       </x:c>
       <x:c r="F40" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:6">
       <x:c r="A41" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>313</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E41" s="1">
         <x:v>15000</x:v>
       </x:c>
       <x:c r="F41" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:6">
       <x:c r="A42" s="1" t="s">
-        <x:v>608</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>609</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>249</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
         <x:v>12</x:v>
@@ -15004,18 +15004,18 @@
         <x:v>15000</x:v>
       </x:c>
       <x:c r="F42" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:6">
       <x:c r="A43" s="1" t="s">
-        <x:v>605</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>606</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
         <x:v>12</x:v>
@@ -15024,47 +15024,47 @@
         <x:v>15000</x:v>
       </x:c>
       <x:c r="F43" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:6">
       <x:c r="A44" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>628</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>420</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>164</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E44" s="1">
         <x:v>15000</x:v>
       </x:c>
       <x:c r="F44" s="2" t="s">
-        <x:v>57</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:6">
       <x:c r="A45" s="1" t="s">
-        <x:v>247</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>248</x:v>
+        <x:v>628</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>249</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="E45" s="1">
         <x:v>15000</x:v>
       </x:c>
       <x:c r="F45" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:6">
@@ -15144,7 +15144,7 @@
         <x:v>12917</x:v>
       </x:c>
       <x:c r="F49" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:6">
@@ -16364,7 +16364,7 @@
         <x:v>5000</x:v>
       </x:c>
       <x:c r="F110" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:6">
@@ -16544,7 +16544,7 @@
         <x:v>5000</x:v>
       </x:c>
       <x:c r="F119" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:6">
@@ -16644,7 +16644,7 @@
         <x:v>5000</x:v>
       </x:c>
       <x:c r="F124" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:6">
@@ -16884,7 +16884,7 @@
         <x:v>5000</x:v>
       </x:c>
       <x:c r="F136" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:6">
@@ -17004,7 +17004,7 @@
         <x:v>5000</x:v>
       </x:c>
       <x:c r="F142" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:6">
@@ -17024,7 +17024,7 @@
         <x:v>5000</x:v>
       </x:c>
       <x:c r="F143" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:6">
@@ -17244,7 +17244,7 @@
         <x:v>5000</x:v>
       </x:c>
       <x:c r="F154" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:6">
@@ -18004,7 +18004,7 @@
         <x:v>2525</x:v>
       </x:c>
       <x:c r="F192" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="193" spans="1:6">
@@ -18044,7 +18044,7 @@
         <x:v>2500</x:v>
       </x:c>
       <x:c r="F194" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="195" spans="1:6">
@@ -19304,7 +19304,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="F257" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="258" spans="1:6">
@@ -20284,7 +20284,7 @@
         <x:v>500</x:v>
       </x:c>
       <x:c r="F306" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="307" spans="1:6">
@@ -20464,7 +20464,7 @@
         <x:v>500</x:v>
       </x:c>
       <x:c r="F315" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="316" spans="1:6">
@@ -20624,7 +20624,7 @@
         <x:v>416</x:v>
       </x:c>
       <x:c r="F323" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="324" spans="1:6">
@@ -20844,7 +20844,7 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="F334" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="335" spans="1:6">
@@ -21350,7 +21350,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H2" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I2" s="1">
         <x:v>5000</x:v>
@@ -21408,7 +21408,7 @@
         <x:v>369</x:v>
       </x:c>
       <x:c r="H4" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I4" s="1">
         <x:v>5000</x:v>
@@ -21440,7 +21440,7 @@
         <x:v>702</x:v>
       </x:c>
       <x:c r="I5" s="1">
-        <x:v>30000</x:v>
+        <x:v>35000</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -21466,10 +21466,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H6" s="2" t="s">
-        <x:v>703</x:v>
+        <x:v>704</x:v>
       </x:c>
       <x:c r="I6" s="1">
-        <x:v>20000</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -21527,7 +21527,7 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="I8" s="1">
-        <x:v>25000</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -21556,7 +21556,7 @@
         <x:v>704</x:v>
       </x:c>
       <x:c r="I9" s="1">
-        <x:v>20000</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -21585,7 +21585,7 @@
         <x:v>702</x:v>
       </x:c>
       <x:c r="I10" s="1">
-        <x:v>30000</x:v>
+        <x:v>35000</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -21614,7 +21614,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="I11" s="1">
-        <x:v>15000</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -21672,7 +21672,7 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="I13" s="1">
-        <x:v>25000</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -21701,7 +21701,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="I14" s="1">
-        <x:v>15000</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -21730,7 +21730,7 @@
         <x:v>702</x:v>
       </x:c>
       <x:c r="I15" s="1">
-        <x:v>30000</x:v>
+        <x:v>35000</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -21759,7 +21759,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="I16" s="1">
-        <x:v>15000</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -21785,7 +21785,7 @@
         <x:v>369</x:v>
       </x:c>
       <x:c r="H17" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>5000</x:v>
@@ -21817,7 +21817,7 @@
         <x:v>704</x:v>
       </x:c>
       <x:c r="I18" s="1">
-        <x:v>20000</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -21846,7 +21846,7 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="I19" s="1">
-        <x:v>25000</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -21875,7 +21875,7 @@
         <x:v>704</x:v>
       </x:c>
       <x:c r="I20" s="1">
-        <x:v>20000</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -21904,7 +21904,7 @@
         <x:v>702</x:v>
       </x:c>
       <x:c r="I21" s="1">
-        <x:v>30000</x:v>
+        <x:v>35000</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -21962,7 +21962,7 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="I23" s="1">
-        <x:v>25000</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -21991,7 +21991,7 @@
         <x:v>704</x:v>
       </x:c>
       <x:c r="I24" s="1">
-        <x:v>20000</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -22020,7 +22020,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="I25" s="1">
-        <x:v>15000</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -22075,7 +22075,7 @@
         <x:v>369</x:v>
       </x:c>
       <x:c r="H27" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>5000</x:v>
@@ -22220,7 +22220,7 @@
         <x:v>619</x:v>
       </x:c>
       <x:c r="H32" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="I32" s="1">
         <x:v>2525</x:v>
@@ -22281,7 +22281,7 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="I34" s="1">
-        <x:v>25000</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -22339,7 +22339,7 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="I36" s="1">
-        <x:v>25000</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -22368,7 +22368,7 @@
         <x:v>702</x:v>
       </x:c>
       <x:c r="I37" s="1">
-        <x:v>30000</x:v>
+        <x:v>35000</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -22423,7 +22423,7 @@
         <x:v>369</x:v>
       </x:c>
       <x:c r="H39" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I39" s="1">
         <x:v>5000</x:v>
@@ -22455,7 +22455,7 @@
         <x:v>704</x:v>
       </x:c>
       <x:c r="I40" s="1">
-        <x:v>20000</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -22484,7 +22484,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="I41" s="1">
-        <x:v>15000</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -22568,7 +22568,7 @@
         <x:v>369</x:v>
       </x:c>
       <x:c r="H44" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I44" s="1">
         <x:v>5000</x:v>
@@ -22597,7 +22597,7 @@
         <x:v>126</x:v>
       </x:c>
       <x:c r="H45" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="I45" s="1">
         <x:v>5000</x:v>
@@ -22626,7 +22626,7 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="H46" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="I46" s="1">
         <x:v>5000</x:v>
@@ -22803,7 +22803,7 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="I52" s="1">
-        <x:v>25000</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
@@ -22858,7 +22858,7 @@
         <x:v>369</x:v>
       </x:c>
       <x:c r="H54" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I54" s="1">
         <x:v>5000</x:v>
@@ -22890,7 +22890,7 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="I55" s="1">
-        <x:v>25000</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:9">
@@ -22948,7 +22948,7 @@
         <x:v>702</x:v>
       </x:c>
       <x:c r="I57" s="1">
-        <x:v>30000</x:v>
+        <x:v>35000</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:9">
@@ -22977,7 +22977,7 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="I58" s="1">
-        <x:v>25000</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:9">
@@ -23006,7 +23006,7 @@
         <x:v>704</x:v>
       </x:c>
       <x:c r="I59" s="1">
-        <x:v>20000</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:9">
@@ -23035,7 +23035,7 @@
         <x:v>702</x:v>
       </x:c>
       <x:c r="I60" s="1">
-        <x:v>30000</x:v>
+        <x:v>35000</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:9">
@@ -23064,7 +23064,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="I61" s="1">
-        <x:v>15000</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:9">
@@ -23093,7 +23093,7 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="I62" s="1">
-        <x:v>25000</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:9">
@@ -23122,7 +23122,7 @@
         <x:v>704</x:v>
       </x:c>
       <x:c r="I63" s="1">
-        <x:v>20000</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:9">
@@ -23151,7 +23151,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="I64" s="1">
-        <x:v>15000</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:9">
@@ -23180,7 +23180,7 @@
         <x:v>702</x:v>
       </x:c>
       <x:c r="I65" s="1">
-        <x:v>30000</x:v>
+        <x:v>35000</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:9">
@@ -23238,7 +23238,7 @@
         <x:v>702</x:v>
       </x:c>
       <x:c r="I67" s="1">
-        <x:v>30000</x:v>
+        <x:v>35000</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:9">
@@ -23267,7 +23267,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="I68" s="1">
-        <x:v>15000</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:9">
@@ -23296,7 +23296,7 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="I69" s="1">
-        <x:v>25000</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:9">
@@ -23325,7 +23325,7 @@
         <x:v>704</x:v>
       </x:c>
       <x:c r="I70" s="1">
-        <x:v>20000</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:9">
@@ -23354,7 +23354,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="I71" s="1">
-        <x:v>15000</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:9">
@@ -23383,7 +23383,7 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="I72" s="1">
-        <x:v>25000</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:9">
@@ -23412,7 +23412,7 @@
         <x:v>704</x:v>
       </x:c>
       <x:c r="I73" s="1">
-        <x:v>20000</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:9">
@@ -23470,7 +23470,7 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="I75" s="1">
-        <x:v>25000</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:9">
@@ -23525,7 +23525,7 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="H77" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="I77" s="1">
         <x:v>5000</x:v>
@@ -23557,7 +23557,7 @@
         <x:v>702</x:v>
       </x:c>
       <x:c r="I78" s="1">
-        <x:v>30000</x:v>
+        <x:v>35000</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:9">
@@ -23586,7 +23586,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="I79" s="1">
-        <x:v>15000</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:9">
@@ -23615,7 +23615,7 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="I80" s="1">
-        <x:v>25000</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:9">
@@ -23641,7 +23641,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="H81" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="I81" s="1">
         <x:v>2500</x:v>
@@ -23728,7 +23728,7 @@
         <x:v>369</x:v>
       </x:c>
       <x:c r="H84" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I84" s="1">
         <x:v>5000</x:v>
@@ -23818,7 +23818,7 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="I87" s="1">
-        <x:v>25000</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:9">
@@ -23876,7 +23876,7 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="I89" s="1">
-        <x:v>25000</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:9">
@@ -23989,7 +23989,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H93" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I93" s="1">
         <x:v>5000</x:v>
@@ -24018,7 +24018,7 @@
         <x:v>369</x:v>
       </x:c>
       <x:c r="H94" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I94" s="1">
         <x:v>5000</x:v>
@@ -24050,7 +24050,7 @@
         <x:v>704</x:v>
       </x:c>
       <x:c r="I95" s="1">
-        <x:v>20000</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:9">
@@ -24108,7 +24108,7 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="I97" s="1">
-        <x:v>25000</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:9">
@@ -24311,7 +24311,7 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="I104" s="1">
-        <x:v>25000</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:9">
@@ -24340,7 +24340,7 @@
         <x:v>702</x:v>
       </x:c>
       <x:c r="I105" s="1">
-        <x:v>30000</x:v>
+        <x:v>35000</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:9">
@@ -24369,7 +24369,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="I106" s="1">
-        <x:v>15000</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:9">
@@ -24398,7 +24398,7 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="I107" s="1">
-        <x:v>25000</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:9">
@@ -24424,7 +24424,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H108" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I108" s="1">
         <x:v>5000</x:v>
@@ -24453,7 +24453,7 @@
         <x:v>369</x:v>
       </x:c>
       <x:c r="H109" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I109" s="1">
         <x:v>5000</x:v>
@@ -24485,7 +24485,7 @@
         <x:v>704</x:v>
       </x:c>
       <x:c r="I110" s="1">
-        <x:v>20000</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:9">
@@ -24514,7 +24514,7 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="I111" s="1">
-        <x:v>25000</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:9">
@@ -24543,7 +24543,7 @@
         <x:v>704</x:v>
       </x:c>
       <x:c r="I112" s="1">
-        <x:v>20000</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:9">
@@ -24572,7 +24572,7 @@
         <x:v>702</x:v>
       </x:c>
       <x:c r="I113" s="1">
-        <x:v>30000</x:v>
+        <x:v>35000</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:9">
@@ -24627,10 +24627,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H115" s="2" t="s">
-        <x:v>703</x:v>
+        <x:v>704</x:v>
       </x:c>
       <x:c r="I115" s="1">
-        <x:v>20000</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:9">
@@ -24688,7 +24688,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="I117" s="1">
-        <x:v>15000</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:9">
@@ -24717,7 +24717,7 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="I118" s="1">
-        <x:v>25000</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:9">
@@ -24746,7 +24746,7 @@
         <x:v>704</x:v>
       </x:c>
       <x:c r="I119" s="1">
-        <x:v>20000</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:9">
@@ -24772,7 +24772,7 @@
         <x:v>126</x:v>
       </x:c>
       <x:c r="H120" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="I120" s="1">
         <x:v>5000</x:v>
@@ -24801,7 +24801,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="H121" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="I121" s="1">
         <x:v>5000</x:v>
@@ -24830,7 +24830,7 @@
         <x:v>126</x:v>
       </x:c>
       <x:c r="H122" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="I122" s="1">
         <x:v>5000</x:v>
@@ -24862,7 +24862,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="I123" s="1">
-        <x:v>15000</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:9">
@@ -24888,7 +24888,7 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="H124" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="I124" s="1">
         <x:v>5000</x:v>
@@ -24920,7 +24920,7 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="I125" s="1">
-        <x:v>25000</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:9">
@@ -24949,7 +24949,7 @@
         <x:v>704</x:v>
       </x:c>
       <x:c r="I126" s="1">
-        <x:v>20000</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:9">
@@ -24978,7 +24978,7 @@
         <x:v>702</x:v>
       </x:c>
       <x:c r="I127" s="1">
-        <x:v>30000</x:v>
+        <x:v>35000</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:9">
@@ -25004,10 +25004,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H128" s="2" t="s">
-        <x:v>703</x:v>
+        <x:v>704</x:v>
       </x:c>
       <x:c r="I128" s="1">
-        <x:v>20000</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:9">
@@ -25065,7 +25065,7 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="I130" s="1">
-        <x:v>25000</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:9">
@@ -25094,7 +25094,7 @@
         <x:v>704</x:v>
       </x:c>
       <x:c r="I131" s="1">
-        <x:v>20000</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:9">
@@ -25123,7 +25123,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="I132" s="1">
-        <x:v>15000</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:9">
@@ -25152,7 +25152,7 @@
         <x:v>702</x:v>
       </x:c>
       <x:c r="I133" s="1">
-        <x:v>30000</x:v>
+        <x:v>35000</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:9">
@@ -25207,7 +25207,7 @@
         <x:v>369</x:v>
       </x:c>
       <x:c r="H135" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I135" s="1">
         <x:v>5000</x:v>
@@ -25239,7 +25239,7 @@
         <x:v>704</x:v>
       </x:c>
       <x:c r="I136" s="1">
-        <x:v>20000</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:9">
@@ -25268,7 +25268,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="I137" s="1">
-        <x:v>15000</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:9">
@@ -25326,7 +25326,7 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="I139" s="1">
-        <x:v>25000</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:9">
@@ -25355,7 +25355,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="I140" s="1">
-        <x:v>15000</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:9">
@@ -25384,7 +25384,7 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="I141" s="1">
-        <x:v>25000</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:9">
@@ -25471,7 +25471,7 @@
         <x:v>702</x:v>
       </x:c>
       <x:c r="I144" s="1">
-        <x:v>30000</x:v>
+        <x:v>35000</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:9">
@@ -25558,7 +25558,7 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="I147" s="1">
-        <x:v>25000</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:9">
@@ -25616,7 +25616,7 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="I149" s="1">
-        <x:v>25000</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:9">
@@ -25645,7 +25645,7 @@
         <x:v>702</x:v>
       </x:c>
       <x:c r="I150" s="1">
-        <x:v>30000</x:v>
+        <x:v>35000</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:9">
@@ -25671,7 +25671,7 @@
         <x:v>369</x:v>
       </x:c>
       <x:c r="H151" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I151" s="1">
         <x:v>5000</x:v>
@@ -25729,7 +25729,7 @@
         <x:v>619</x:v>
       </x:c>
       <x:c r="H153" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="I153" s="1">
         <x:v>2525</x:v>
@@ -25790,7 +25790,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="I155" s="1">
-        <x:v>15000</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:9">
@@ -25819,7 +25819,7 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="I156" s="1">
-        <x:v>25000</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:9">
@@ -25848,7 +25848,7 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="I157" s="1">
-        <x:v>25000</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -26977,36 +26977,36 @@
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>734</x:v>
+        <x:v>812</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>735</x:v>
+        <x:v>813</x:v>
       </x:c>
       <x:c r="C3" s="1">
-        <x:v>23666</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="D3" s="1">
-        <x:v>84670</x:v>
+        <x:v>36350</x:v>
       </x:c>
       <x:c r="E3" s="1">
-        <x:v>27.950868</x:v>
+        <x:v>27.510316</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>812</x:v>
+        <x:v>734</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>813</x:v>
+        <x:v>735</x:v>
       </x:c>
       <x:c r="C4" s="1">
-        <x:v>10000</x:v>
+        <x:v>23666</x:v>
       </x:c>
       <x:c r="D4" s="1">
-        <x:v>36350</x:v>
+        <x:v>90320</x:v>
       </x:c>
       <x:c r="E4" s="1">
-        <x:v>27.510316</x:v>
+        <x:v>26.202391</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
@@ -27088,10 +27088,10 @@
         <x:v>11500</x:v>
       </x:c>
       <x:c r="D9" s="1">
-        <x:v>125540</x:v>
+        <x:v>129267</x:v>
       </x:c>
       <x:c r="E9" s="1">
-        <x:v>9.160426</x:v>
+        <x:v>8.896315</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
@@ -27564,10 +27564,10 @@
         <x:v>1500</x:v>
       </x:c>
       <x:c r="D37" s="1">
-        <x:v>226722</x:v>
+        <x:v>226872</x:v>
       </x:c>
       <x:c r="E37" s="1">
-        <x:v>0.661603</x:v>
+        <x:v>0.661165</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:5">
@@ -27844,36 +27844,36 @@
     </x:row>
     <x:row r="54" spans="1:5">
       <x:c r="A54" s="1" t="s">
-        <x:v>784</x:v>
+        <x:v>708</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>785</x:v>
+        <x:v>709</x:v>
       </x:c>
       <x:c r="C54" s="1">
-        <x:v>1000</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="D54" s="1">
-        <x:v>426916</x:v>
+        <x:v>350411</x:v>
       </x:c>
       <x:c r="E54" s="1">
-        <x:v>0.234238</x:v>
+        <x:v>0.214034</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:5">
       <x:c r="A55" s="1" t="s">
-        <x:v>708</x:v>
+        <x:v>784</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>709</x:v>
+        <x:v>785</x:v>
       </x:c>
       <x:c r="C55" s="1">
-        <x:v>750</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D55" s="1">
-        <x:v>350411</x:v>
+        <x:v>531836</x:v>
       </x:c>
       <x:c r="E55" s="1">
-        <x:v>0.214034</x:v>
+        <x:v>0.188027</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:5">
